--- a/results/job_matches_2026-10-19.xlsx
+++ b/results/job_matches_2026-10-19.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Westley Resource</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -474,85 +474,120 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203d1d5d70a09d61</t>
+          <t>https://www.indeed.com/viewjob?jk=92800e8ae0ec90fd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Collaboration Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Walt Disney Studios</t>
+          <t>Mindos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Burbank, CA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a305eedaa5ea3e71</t>
+          <t>https://www.indeed.com/viewjob?jk=12f39cbbefa0dc98</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Walt Disney Studios</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Burbank, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a305eedaa5ea3e71</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Data Pipeline Engineer — Apache Airflow (Astronomer) &amp; Python</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Triade Flevoland</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Remote, USA USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>11.8</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>AWS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=41823bf35722426c</t>
         </is>

--- a/results/job_matches_2026-10-19.xlsx
+++ b/results/job_matches_2026-10-19.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,25 +491,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Collaboration Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mindos</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>IL, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12f39cbbefa0dc98</t>
+          <t>https://www.indeed.com/viewjob?jk=6f7b2d8efc3f839d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Walt Disney Studios</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Burbank, CA, USA USA</t>
+          <t>NJ, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,52 +544,262 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a305eedaa5ea3e71</t>
+          <t>https://www.indeed.com/viewjob?jk=a719323347467085</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Walt Disney Studios</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Burbank, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a305eedaa5ea3e71</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ME, USA USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75edeac96c9cb9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, USA USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Snowflake, Oracle, MongoDB, ELT, CI/CD, Jenkins, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f3d89fb837011e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Engineer – Azure Databricks and Cloud Data Solutions (Safety)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Southern Company</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, USA USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7758a0009c0207a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trading Technologies</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba95ea6670a9b3d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Data Pipeline Engineer — Apache Airflow (Astronomer) &amp; Python</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Triade Flevoland</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Remote, USA USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D10" t="n">
         <v>11.8</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>AWS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=41823bf35722426c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Solution Architect - Data</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SANTEE COOPER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Moncks Corner, SC, USA USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0dc4750fd2d1381</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-19.xlsx
+++ b/results/job_matches_2026-10-19.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Databricks Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -501,15 +501,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IL, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f7b2d8efc3f839d</t>
+          <t>https://www.indeed.com/viewjob?jk=9487189cf1ce078a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,42 +554,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a719323347467085</t>
+          <t>https://www.indeed.com/viewjob?jk=66bbf18d8af2a6ff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Databricks Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Walt Disney Studios</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Burbank, CA, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a305eedaa5ea3e71</t>
+          <t>https://www.indeed.com/viewjob?jk=0b06c504c630d06c</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ME, USA USA</t>
+          <t>VA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75edeac96c9cb9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=93a8b56d1860b57b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, USA USA</t>
+          <t>GA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Snowflake, Oracle, MongoDB, ELT, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f3d89fb837011e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7238ddca48d3e867</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer – Azure Databricks and Cloud Data Solutions (Safety)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>The Walt Disney Studios</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Birmingham, AL, USA USA</t>
+          <t>Burbank, CA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7758a0009c0207a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a305eedaa5ea3e71</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trading Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,77 +729,532 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba95ea6670a9b3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=af6af62a6d02e79a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Pipeline Engineer — Apache Airflow (Astronomer) &amp; Python</t>
+          <t>Analytics Engineer, Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Triade Flevoland</t>
+          <t>Integrity Express Logistics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Data Factory, Scala, Snowflake, PostgreSQL, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41823bf35722426c</t>
+          <t>https://www.indeed.com/viewjob?jk=67b743d65f4b7d93</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Full Stack Java Developer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Techsur Solutions</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Reston, VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62a75c0bc2ea3dff</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Healthix</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4f218e26bf82748</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer – Azure Databricks and Cloud Data Solutions (Safety)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Southern Company</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, USA USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7758a0009c0207a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DevOps Machine Learning Infrastructure</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Syntiant Corp</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9b6d2e723c537f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, USA USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Snowflake, Oracle, MongoDB, ELT, CI/CD, Jenkins, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f3d89fb837011e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Trading Technologies</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba95ea6670a9b3d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Pipeline Engineer — Apache Airflow (Astronomer) &amp; Python</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Triade Flevoland</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41823bf35722426c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cloud Systems Administrator and Developer II</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JMARK Business Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Springfield, MO, USA USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93db17295ea8644d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Analyst, Data Engineer, Firehouse Subs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Firehouse Subs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a48e0afee3045f50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Irving, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7e9a2aa1706c94b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DevOps Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=663a25b79e0b53be</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DevOps Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56016491aa37bf6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Solution Architect - Data</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>SANTEE COOPER</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Moncks Corner, SC, USA USA</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D23" t="n">
         <v>11.1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0dc4750fd2d1381</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Marketing Enablement Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Miami, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26ba939799dd2e43</t>
         </is>
       </c>
     </row>
